--- a/02_Excel_Analytics_Nhi.xlsx
+++ b/02_Excel_Analytics_Nhi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2a75de9baa28f32/Máy tính/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CE5DE05-19EB-484A-9272-1D9CFBD182DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{7CE5DE05-19EB-484A-9272-1D9CFBD182DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE1C9C20-41A2-44FA-AF84-BBAC85E50345}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4FE78D82-9F18-4F04-99DB-24E87CEE862F}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>B2504903</t>
   </si>
   <si>
-    <t>Ly Nhat Vy</t>
-  </si>
-  <si>
     <t>Security &amp; Digital Health</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Total Count</t>
+  </si>
+  <si>
+    <t>Ly Nhat Vy(1)</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Book1.xlsx]Sheet1!PivotTable2</c:name>
+    <c:name>[02_Excel_Analytics_Nhi.xlsx]Sheet1!PivotTable2</c:name>
     <c:fmtId val="15"/>
   </c:pivotSource>
   <c:chart>
@@ -2110,22 +2110,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" t="s">
         <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2142,7 +2142,7 @@
         <v>46106</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -2152,7 +2152,7 @@
         <v>Nguyen Thi Ngoc Tram</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -2172,10 +2172,10 @@
         <v>46113</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -2195,10 +2195,10 @@
         <v>46103</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -2218,7 +2218,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
@@ -2226,16 +2226,16 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="4">
         <v>46116</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/02_Excel_Analytics_Nhi.xlsx
+++ b/02_Excel_Analytics_Nhi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2a75de9baa28f32/Máy tính/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{7CE5DE05-19EB-484A-9272-1D9CFBD182DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE1C9C20-41A2-44FA-AF84-BBAC85E50345}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7CE5DE05-19EB-484A-9272-1D9CFBD182DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{021CEF18-F2F2-4D66-8824-5C313AC655F8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4FE78D82-9F18-4F04-99DB-24E87CEE862F}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>B2504888</t>
   </si>
   <si>
-    <t>Le Nguyen Ngoc Nhi</t>
-  </si>
-  <si>
     <t>Excel Analytics</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Ly Nhat Vy(1)</t>
+  </si>
+  <si>
+    <t>Le Nguyen Ngoc Nhi(2)</t>
   </si>
 </sst>
 </file>
@@ -2110,22 +2110,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" t="s">
         <v>24</v>
-      </c>
-      <c r="K1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2142,40 +2142,40 @@
         <v>46106</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="str">
         <f>VLOOKUP(G2, $A$2:$B6, 2, 0)</f>
         <v>Nguyen Thi Ngoc Tram</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="4">
         <v>46113</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -2183,22 +2183,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="4">
         <v>46103</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -2206,36 +2206,36 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="4">
         <v>46108</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>46116</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
